--- a/public/exports/29189730.xlsx
+++ b/public/exports/29189730.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -5989,7 +5989,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706715</t>
+          <t xml:space="preserve">311706717</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -7939,12 +7939,12 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311710301</t>
+          <t xml:space="preserve">311710302</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311710293</t>
+          <t xml:space="preserve">311710302</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M109" t="inlineStr">

--- a/public/exports/29189730.xlsx
+++ b/public/exports/29189730.xlsx
@@ -5989,7 +5989,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706717</t>
+          <t xml:space="preserve">311706715</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -6589,7 +6589,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706709</t>
+          <t xml:space="preserve">311706968</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -7864,12 +7864,12 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311710302</t>
+          <t xml:space="preserve">311710303</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -7939,12 +7939,12 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311710302</t>
+          <t xml:space="preserve">311710301</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -8014,12 +8014,12 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311710302</t>
+          <t xml:space="preserve">311710304</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -8089,12 +8089,12 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311710302</t>
+          <t xml:space="preserve">311710306</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311710302</t>
+          <t xml:space="preserve">311710293</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">

--- a/public/exports/29189730.xlsx
+++ b/public/exports/29189730.xlsx
@@ -6589,7 +6589,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706968</t>
+          <t xml:space="preserve">311706709</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -7864,12 +7864,12 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311710303</t>
+          <t xml:space="preserve">311710302</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -8014,12 +8014,12 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311710304</t>
+          <t xml:space="preserve">311710302</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -8089,12 +8089,12 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311710306</t>
+          <t xml:space="preserve">311710302</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M108" t="inlineStr">
